--- a/mode_docx_gen/pmi_mtzt/bnt_modes/БНТ_10.xlsx
+++ b/mode_docx_gen/pmi_mtzt/bnt_modes/БНТ_10.xlsx
@@ -1318,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>gen_pusk_ptoc_lvttoc</t>
+          <t>gen_pusk_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
